--- a/spreadsheet/aviva.xlsx
+++ b/spreadsheet/aviva.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,13 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -57,15 +64,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -428,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -453,7 +465,2439 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AVI Japan Opportunity Ord</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GB00BD6H5D36</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000011E3X/GB00BD6H5D36</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aberdeen Asia Focus PLC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GB00BMF19B58</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR06XED/GB00BMF19B58</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aberdeen Asian Income Fund Limited</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GB00B0P6J834</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0000008V0/GB00B0P6J834</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aberdeen Equity Income Trust</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GB0006039597</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01O5X/GB0006039597</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aberdeen New India Investment Trust</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GB0006048770</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01PW0/GB0006048770</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aberdeen UK Smaller Cos Growth Trust plc</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GB0002959582</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01NOZ/GB0002959582</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aberforth Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GB0000066554</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01NFP/GB0000066554</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Alliance Witan Ord</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GB00B11V7W98</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00QKW/GB00B11V7W98</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Allianz Technology Trust Ord</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GB00BNG2M159</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR053PH/GB00BNG2M159</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Artemis UK Future Leaders Ord</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GB00B1FL3C76</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR052P3/GB00B1FL3C76</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ashoka India Equity Investment Ord</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GB00BF50VS41</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000010R57/GB00BF50VS41</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aurora UK Alpha Ord</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GB0000633262</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR04AOE/GB0000633262</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Baillie Gifford China Growth Trust Ord</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GB0003656021</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR017H2/GB0003656021</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Baillie Gifford European Growth Ord</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GB00BMC7T380</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00VWL/GB00BMC7T380</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Japan Ord</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GB0000485838</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00R22/GB0000485838</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Shin Nippon Ord</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GB00BFXYH242</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR003A8/GB00BFXYH242</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Baillie Gifford UK Growth Trust Ord</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GB0007913485</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01O8T/GB0007913485</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Baillie Gifford US Growth Ord</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GB00BDFGHW41</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0000109JH/GB00BDFGHW41</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Bankers Ord</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GB00BN4NDR39</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR051W1/GB00BN4NDR39</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Biotech Growth Ord</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GB0000385517</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR053PF/GB0000385517</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BlackRock American Income Trust Ord</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GB00B7W0XJ61</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000OUTA/GB00B7W0XJ61</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BlackRock Energy and Resources Inc</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GB00B0N8MF98</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000EYO/GB00B0N8MF98</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BlackRock Frontiers Ord</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GB00B3SXM832</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000LN8Y/GB00B3SXM832</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BlackRock Greater Europe Ord</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GB00B01RDH75</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000EYP/GB00B01RDH75</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BlackRock Income and Growth Ord</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GB0030961691</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR052QA/GB0030961691</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BlackRock Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GB0006436108</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01ORG/GB0006436108</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BlackRock World Mining Trust Ord</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GB0005774855</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01OPI/GB0005774855</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Brown Advisory US Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GB0003463402</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR052PF/GB0003463402</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Brunner Ord</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GB0001490001</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR051X2/GB0001490001</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CC Japan Income &amp; Growth Ord</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GB00BYSRMH16</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000WLWG/GB00BYSRMH16</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CQS New City High Yield Ord</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JE00B1LZS514</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000EOU/JE00B1LZS514</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CT Private Equity Trust Ord</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GB0030738271</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000EW8/GB0030738271</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CT UK Capital and Income Ord</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GB0003463287</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01OSP/GB0003463287</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CT UK High Income Ord</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GB00B1N4G299</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0000026LU/GB00B1N4G299</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CVC Income &amp; Growth GBP</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>JE00B9MRHZ51</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000Q2Q8/JE00B9MRHZ51</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Caledonia Investments Ord</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GB00BTNQ8K38</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00490/GB00BTNQ8K38</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Capital Gearing Ord</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GB0001738615</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR004CX/GB0001738615</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chelverton UK Dividend Trust Ord</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GB0006615826</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01PR6/GB0006615826</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>City of London Ord</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GB0001990497</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00QXA/GB0001990497</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Custodian Property Income REIT Ord</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GB00BJFLFT45</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000T1SI/GB00BJFLFT45</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Digital 9 Infrastructure Ord</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>JE00BPH3HM76</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000016Q2H/JE00BPH3HM76</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Diverse Income Trust Ord</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GB00B65TLW28</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000MILK/GB00B65TLW28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dunedin Income Growth Ord</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>GB0003406096</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00V7N/GB0003406096</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ecofin Global Utilities &amp; Infra Ord</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>GB00BD3V4641</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000XRIZ/GB00BD3V4641</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Edinburgh Investment Ord</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GB0003052338</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR051V5/GB0003052338</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Edinburgh Worldwide Ord</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GB00BHSRZC82</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01OFW/GB00BHSRZC82</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>European Opportunities Trust</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GB0000197722</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01DOK/GB0000197722</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>F&amp;C Investment Trust Ord</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GB00BS88V647</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR052PD/GB00BS88V647</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Fidelity Asian Values Ord</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GB0003322319</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR04E6W/GB0003322319</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Fidelity China Special Situations Ord</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>GB00B62Z3C74</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000H0Q7/GB00B62Z3C74</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fidelity Emerging Markets Ord</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GG00B4L0PD47</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000005MI9/GG00B4L0PD47</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Fidelity European Trust Ord</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>GB00BK1PKQ95</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR04E70/GB00BK1PKQ95</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Fidelity Special Values Ord</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GB00BWXC7Y93</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR04E7U/GB00BWXC7Y93</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Finsbury Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>GB0007816068</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR053PE/GB0007816068</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Foresight Environmental Infra Ord</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GG00BJL5FH87</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000T0X0/GG00BJL5FH87</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Global Opportunities Trust Ord</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GB0033862573</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000EYD/GB0033862573</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Gore Street Energy Storage Fund Ord</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GB00BG0P0V73</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000010CWU/GB00BG0P0V73</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Greencoat UK Wind</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GB00B8SC6K54</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000PPTR/GB00B8SC6K54</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>HICL Infrastructure PLC Ord</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>GB00BJLP1Y77</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0000008ZF/GB00BJLP1Y77</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Henderson Far East Income Ord</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>JE00B1GXH751</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00QXD/JE00B1GXH751</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Henderson High Income Ord</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>GB0009580571</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00QXE/GB0009580571</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Henderson Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GB0009065060</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00J99/GB0009065060</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Herald Ord</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>GB0004228648</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01NLR/GB0004228648</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ICG Enterprise Trust Ord</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>GB0003292009</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00VWK/GB0003292009</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Impax Environmental Markets Ord</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GB0031232498</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01R9F/GB0031232498</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>India Capital Growth Ord</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>GB00B0P8RJ60</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000DUI/GB00B0P8RJ60</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>International Biotechnology Ord</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GB0004559349</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR04Y7C/GB0004559349</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Invesco Asia Dragon Trust Ord</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GB0004535307</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR052RM/GB0004535307</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Invesco Bond Income Plus Ord</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>JE00B6RMDP68</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR04ATI/JE00B6RMDP68</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Invesco Global Equity Income Trust ord</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>GB00B1DQ6472</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000EWC/GB00B1DQ6472</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>JPMorgan American Ord</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>GB00BKZGVH64</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01ABF/GB00BKZGVH64</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>JPMorgan Asia Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>GB0001320778</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00Y7H/GB0001320778</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>JPMorgan China Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>GB0003435012</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01Q4P/GB0003435012</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>JPMorgan Claverhouse Ord</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GB0003422184</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01ABG/GB0003422184</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>JPMorgan Emerg EMEA Sec Plc</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GB0032164732</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR06X0O/GB0032164732</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>JPMorgan Emerging Markets Div Inc</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GB00B5ZZY915</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000J8GU/GB00B5ZZY915</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>JPMorgan Emerging Markets Growth &amp; Inc</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GB00BMXWN182</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000JUY/GB00BMXWN182</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>JPMorgan European Discovery Ord</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>GB00BMTS0Z37</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00VWD/GB00BMTS0Z37</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>JPMorgan European Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>GB00BPR9Y246</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000EWI/GB00BPR9Y246</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>JPMorgan Global Core Real Assets Ord</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GG00BWPKR307</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0000146Y9/GG00BWPKR307</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>JPMorgan Global Growth &amp; Income Ord</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>GB00BYMKY695</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00VWJ/GB00BYMKY695</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>JPMorgan India Growth &amp; Income plc</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GB0003450359</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01O5D/GB0003450359</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>JPMorgan Japanese Ord</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GB0001740025</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00P1D/GB0001740025</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>JPMorgan UK Small Cap Growth &amp; Income</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GB00BF7L8P11</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00VGD/GB00BF7L8P11</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>JPMorgan US Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>GB00BJL5F346</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00VWF/GB00BJL5F346</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Law Debenture Corporation Ord</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>GB0031429219</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR0098P/GB0031429219</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Lindsell Train Ord</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>GB00BNKDVV71</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01Q73/GB00BNKDVV71</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Lowland Ord</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GB00BNXGHS27</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR009GD/GB00BNXGHS27</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MIGO Opportunities Trust Ord</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>GB0034365949</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000E8Q/GB0034365949</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Majedie Investments Ord</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>GB0005555221</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR009LZ/GB0005555221</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Mercantile Ord</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>GB00BF4JDH58</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00VWI/GB00BF4JDH58</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Merchants Trust Ord</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>GB0005800072</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR051XC/GB0005800072</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mid Wynd International Inv Tr Ord</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GB00B6VTTK07</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000EYQ/GB00B6VTTK07</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Mobius Investment Trust Ord</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GB00BFZ7R980</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0000119CQ/GB00BFZ7R980</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Monks Ord</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GB0030517261</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00PWQ/GB0030517261</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Montanaro European Smaller Ord</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GB00BM8H3X05</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01Q40/GB00BM8H3X05</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Montanaro UK Smaller Companies Ord</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>GB00BZ1H9L86</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR06NZS/GB00BZ1H9L86</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Murray Income Trust Ord</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>GB0006111123</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00V35/GB0006111123</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Murray International Ord</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GB00BQZCCB79</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00V37/GB00BQZCCB79</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>North American Income Trust Ord</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>GB00BJ00Z303</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR002Q1/GB00BJ00Z303</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Pacific Assets Ord</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GB0006674385</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01P3I/GB0006674385</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Pacific Horizon Ord</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GB0006667470</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00QB2/GB0006667470</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Pantheon Infrastructure Ord</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GB00BLNNFL88</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00001D0H1/GB00BLNNFL88</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Pantheon International Ord</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>GB00BP37WF17</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00QBC/GB00BP37WF17</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Patria Private Equity Trust</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>GB0030474687</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR04AQV/GB0030474687</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Personal Assets Ord</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>GB00BM8B5H06</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01KRI/GB00BM8B5H06</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Polar Capital Glb Healthcare Ord</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>GB00B6832P16</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000IT4M/GB00B6832P16</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Polar Capital Global Financials Ord</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>GB00B9XQT119</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000Q195/GB00B9XQT119</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Polar Capital Technology Ord</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>GB00BR3YV268</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00VIE/GB00BR3YV268</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>RIT Capital Partners Ord</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>GB0007366395</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00BUS/GB0007366395</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Schroder AsiaPacific Ord</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GB0007918872</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01N9E/GB0007918872</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Schroder Asian Total Return Inv. Company</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>GB0008710799</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00QXF/GB0008710799</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Schroder BSC Social Impact Trust Ord</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GB00BF781319</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0000168SP/GB00BF781319</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Schroder European Real Estate Inv Trust</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GB00BY7R8K77</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000WM3Z/GB00BY7R8K77</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Schroder Income Growth Ord</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GB0007915860</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01NNO/GB0007915860</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Schroder Japan Trust Ord</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GB0008022849</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01NIU/GB0008022849</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Schroder Oriental Income Ord</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>GB00B0CRWN59</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0000008UY/GB00B0CRWN59</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Schroder UK Mid Cap Ord</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>GB0006108418</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00A9W/GB0006108418</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Schroders Capital Global Innov Trust Ord</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>GB00BVG1CF25</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000VFUD/GB00BVG1CF25</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Scottish American Ord</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>GB0007873697</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00CND/GB0007873697</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Scottish Mortgage Ord</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>GB00BLDYK618</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00R1S/GB00BLDYK618</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Scottish Oriental Smaller Cos Ord</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>GB00BRBL6574</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR04AN0/GB00BRBL6574</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Seraphim Space Investment Trust Ord</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GB00BKPG0138</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00001A8YM/GB00BKPG0138</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Social Housing REIT Ord</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GB00BF0P7H59</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000ZDP6/GB00BF0P7H59</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Strategic Equity Capital Ord</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GB00B0BDCB21</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000EZ0/GB00B0BDCB21</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TR Property Ord</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GB0009064097</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00QXG/GB0009064097</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Target Healthcare REIT Ord</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GB00BJGTLF51</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000Q5EH/GB00BJGTLF51</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Temple Bar Ord</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GB00BMV92D64</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR00J8R/GB00BMV92D64</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Templeton Emerging Mkts Invmt Tr TEMIT</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>GB00BKPG0S09</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR05WML/GB00BKPG0S09</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>The European Smaller Companies Trust PLC</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>GB00BMCF8689</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR06XF5/GB00BMCF8689</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>The Global Smaller Companies Trust Ord</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>GB00BKLXD974</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR006SY/GB00BKLXD974</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Utilico Emerging Markets Ord</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>GB00BD45S967</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F000000BDC/GB00BD45S967</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Value and Indexed Property Income Ord</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>GB0008484718</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/E0GBR01NFR/GB0008484718</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Worldwide Healthcare Ord</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>GB00BN455J50</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F0GBR053PI/GB00BN455J50</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>abrdn European Logistics Income PLC</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>GB00BD9PXH49</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/InvestmentTrustSearch/InvestmentTrustDetails/F00000ZUFD/GB00BD9PXH49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/spreadsheet/aviva.xlsx
+++ b/spreadsheet/aviva.xlsx
@@ -3686,7 +3686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3711,7 +3711,9767 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>7IM AAP Adventurous Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PB2C7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>7IM AAP Adventurous Class C Income</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PB2B6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>7IM AAP Balanced Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PB379/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>7IM AAP Balanced Class C Income</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PB2V6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7IM AAP Cautious Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMXV854/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7IM AAP Cautious Class C Income</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMXV7D5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7IM AAP Moderately Adventurous Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PB2M7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7IM AAP Moderately Adventurous Class C Income</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PB2K5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7IM AAP Moderately Cautious Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PB216/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7IM AAP Moderately Cautious Class C Income</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PB205/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>7IM Adventurous Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3395800/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7IM Adventurous Class C Income</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3395770/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7IM Balanced Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3395974/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>7IM Balanced Class C Income</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3395929/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7IM Moderately Adventurous Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3395651/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7IM Moderately Adventurous Class C Income</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3395639/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>7IM Moderately Cautious Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3395349/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>7IM Moderately Cautious Class C Income</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3395327/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7IM Pathbuilder 1 Class 1C Accumulation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDPBQ8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7IM Pathbuilder 1 Class 1C Inc Income</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDPC09/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7IM Pathbuilder 2 Class 2 Inc Income</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDPC43/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>7IM Pathbuilder 2 Class 2C Accumulation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDPC32/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>7IM Pathbuilder 3 Class 3C Accumulation</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDPC76/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>7IM Pathbuilder 3 Class C Inc Income</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDPC87/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7IM Pathbuilder 4 Class 4 Acc Accumulation</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDPCC1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7IM Pathbuilder 4 Class 4 Inc Income</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDPCD2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7IM Real Return Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B75MS61/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7IM Responsible Balanced Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1LBFZ8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>7IM Responsible Balanced Class C Income</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1LBG00/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AQR Capital Management AQR Apex UCITS Fund Class C1 Accumulation</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYZN302/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AQR Capital Management AQR Global Risk Parity UCITS Fund Class C1 Accumulation</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BVTW5F3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AQR Capital Management AQR Managed Futures UCITS Fund Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BY4JSV7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AQR Capital Management AQR Managed Futures UCITS Fund Class IAG1F Accumulation</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF4R982/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AQR Capital Management AQR Sustainable Delphi Long-Short Equity UCITS Fund Class IAG1 Accumulation</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD572T9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ARGA IM ARGA Emerging Market Equity Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP41L00/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ARGA IM ARGA European Equity Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BV0VHJ7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ATLAS Infrastructure Partners ATLAS Global Infrastructure UCITS ICAV Series C GBP Hedged Share Class (Acc) Accumulation</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMV29Z6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ATLAS Infrastructure Partners ATLAS Global Infrastructure UCITS ICAV Series C GBP Hedged Share Class (Inc) Income</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMFH485/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ATLAS Infrastructure Partners ATLAS Global Infrastructure UCITS ICAV Series C GBP Unhedged Share Class (Inc) Income</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMFH474/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AXA World Funds SICAVs ACT Clean Economy class F (Hedged) Accumulation</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYWL1T4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AXA World Funds SICAVs Digital Economy Class F (Hedged) Accumulation</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF442T5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AXA World Funds SICAVs Robotech Class F Accumulation</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDFDVS9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Aberforth UK Small Companies ABERFORTH UK SMALL-UNITS-GBP/D Accumulation</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0007272/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Aberforth UK Small Companies ABERFORTH UK SMALL-UNITS-GBP/D Income</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2N9GS7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aegon AM Absolute Return Bond Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6SPX87/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aegon AM Absolute Return Bond Class B Income</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4QJCV3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aegon AM Absolute Return Bond Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6SLQ64/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aegon AM Diversified Growth Fund Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B625LX4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Aegon AM Diversified Monthly Income Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJFLQY6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Aegon AM Diversified Monthly Income Class B Income</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJFLR10/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors (Lux) Food Security Class P Income</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN6RFL1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors (Lux) Global Hi-Tech Growth Class PT Income</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQLQ655/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors (Lux) Green Bond Class H2 GBP Income</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF09XJ1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Best Styles Global AC Equity Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYQ91X8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Best Styles Global AC Equity Class O Accumulation</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYZQV96/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Continental European Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3Q8YX9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Emerging Markets Equity Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B0WDH83/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Emerging Markets Equity class O Accumulation</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYZQV63/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Gilt Yield Class I Income</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3138339/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Index-Linked Gilt Fund Class E Income</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDD4M92/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Index-Linked Gilt Fund Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDD4M69/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Index-Linked Gilt Fund Class W Income</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDD4M70/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK RiskMaster Conservative Multi Asset Class Y Accumulation</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYMVB72/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK RiskMaster Growth Multi Asset Class Y Accumulation</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYMVBC7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK RiskMaster Moderate Multi Asset Class Y Accumulation</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYMVB94/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Strategic Bond Class C Income</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B06T936/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Total Return Asian Equity Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BVYJ2G9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK Total Return Asian Equity Class C Income</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1FRQV5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK UK Listed Equity Income Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP5X398/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK UK Listed Equity Income Class C Income</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B82ZGC2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK UK Opportunities Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8BB944/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Allianz Global Investors UK UK Opportunities class O Accumulation</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYZQQN5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Allspring (Lux) Worldwide Fund Climate Transition Global Equity Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDXPM6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Allspring (Lux) Worldwide Fund Emerging Markets Equity Advantage Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7VDVY7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Allspring (Lux) Worldwide Fund Emerging Markets Equity Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B673C52/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Allspring (Lux) Worldwide Fund Global Equity Enhanced Income Class Z Income</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BM9CNN4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Allspring (Lux) Worldwide Fund U.S. All Cap Growth Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3P0LJ1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Allspring (Lux) Worldwide Fund U.S. All Cap Growth Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8FWGL9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Allspring (Lux) Worldwide Fund U.S. All Cap Growth Class Z Income</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BHY3RK2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Alquity SICAV Asia Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK6YNF1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Alquity SICAV Asia Class Y Accumulation</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BTJRGR3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Alquity SICAV Future World Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK6YNG2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Alquity SICAV Future World Class Y Accumulation</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BTJRGT5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Alquity SICAV Global Impact Class Y Accumulation</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BTJRGQ2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Alquity SICAV Indian Subcontinent Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK6YND9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Alquity SICAV VAM Balanced Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD31LY1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Alquity SICAV VAM Cautious Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD31M26/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Alquity SICAV VAM Growth Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD31MH1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Amati Global Investors WS Amati Global Innovation Fund Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKVF3N7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Amati Global Investors WS Amati Strategic Metals Fund Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMD8NV6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Amati Global Investors WS Amati UK Listed Smaller Companies Fund Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2NG4R3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Amova Asset Management Amova ARK Disruptive Innovation Fund Class D GBP  Accumulation</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN13PS1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Amova Asset Management Amova Asia ex-Japan Fund Class D GBP  Accumulation</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDD0LP9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Amova Asset Management Amova Global Equity Fund Class D GBP  Accumulation</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDD0LM6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Amova Asset Management Amova Japan Value Fund Class A GBP Accumulation</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDB4YG5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Amova Asset Management Amova Japan Value Fund Class D GBP Accumulation</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDD0LS2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Amova Asset Management Amova Japan Value Fund Class D GBP Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF591P8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Artemis Income Class I Income</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PLJJ3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Artemis Monthly Distribution Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B75F9Z6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Artemis Monthly Distribution Class I Income</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6TK3R0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Artemis Short-Dated Global High Yield Bond Class I Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK58WC4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Artemis Short-Dated Global High Yield Bond Class I Hedged Income</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK58WD5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Artemis Short-Duration Strategic Bond Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJXPPH6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Artemis Short-Duration Strategic Bond Class I Income</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJXPPJ8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP European Equity Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PLJD7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP European Equity Class I Hedged  Accumulation</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BR4TV19/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP European Equity Class I Hedged  Income</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BR4TV08/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP European Equity Class I Income</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BR4TTQ0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP Global Emerging Markets Equity Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BW9HL13/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP Global Emerging Markets Equity Class I Income</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BW9HL24/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP Global Emerging Markets Equity Class I Quarterly Income</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMC94C8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP Global Emerging Markets Ex China Equity Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWK9895/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP Global Equity Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PLJP9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP Global Smaller Companies Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B568S20/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Artemis SmartGARP UK Equity Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PLJM6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Artemis Strategic Assets Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3VDD43/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Artemis Strategic Bond Class I Monthly Accumulation</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJT0KV4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Artemis Strategic Bond Class I Monthly Income</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PLJS2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Artemis Strategic Bond Class I Quarterly Accumulation</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PLJR1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Artemis Strategic Bond Class I Quarterly Income</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJT0KT2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Artemis UK Select Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PLJG0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Artemis UK Select Class I Income</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD3GTF3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Artemis UK Smaller Companies Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PLJL5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Artemis UK Smaller Companies Class I Income</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD3GTG4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Artemis UK Special Situations Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PLJQ0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Artemis UK Special Situations Class I Income</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BB36JR1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Artemis US Extended Alpha Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMMV5G5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Artemis US Select Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMMV510/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Artemis US Select Class I Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYSYZX9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Artemis US Select Class I Income</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWWZ2D3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Artemis US Smaller Companies Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMMV576/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Artemis US Smaller Companies Class I Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK6RLD4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Ashmore SICAV Emerging Market Total Return Class Z Income</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BG6M1H5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Ashmore SICAV Emerging Markets Equity Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDDJQ73/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Ashmore SICAV Emerging Markets Short Duration Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYW9P18/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Ashmore SICAV Emerging Markets Short Duration Class Z Income</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP4K8V7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Atlantic House Defensive Defined Returns Class A Accumulation</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDZQTC8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Atlantic House Defined Returns Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFLR220/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Atlantic House Defined Returns Class I Distribution 4% Shares GBP Income</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF2ZW34/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Atlantic House Dynamic Duration Fund Class A GBP Accumulation</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMY8S43/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Atlantic House Dynamic Duration Fund Class D Income</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMY8S54/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Atlantic House Uncorrelated Strategies Class A Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNTJ5Q9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Atlantic House Uncorrelated Strategies Class I Hedged Income</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNTJ5V4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Aubrey Capital Management Ltd Aubrey Global Emerging Markets Opportunities Class RC1 Accumulation</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BZ059L3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Diversified Assets Fund 1 S14</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGGRYT3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Diversified Assets Fund 2 S14</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BLG3441/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Diversified Assets Fund 3 S14</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGGRYV5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2061 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6L2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2062 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6M3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2063 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6N4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2064 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6P6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2065 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6Q7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2066 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6R8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2067 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6S9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2068 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6T0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2069 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6V2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2070 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6W3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2071 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6X4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2072 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6Y5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2073 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT6Z6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2074 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT708/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2075 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT719/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2076 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT720/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2077 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT731/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2078 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT742/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2079 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT753/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2080 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRGT764/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2081 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BSWDG04/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal 2082 Retirement S14</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BT54HZ3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Aviva Insured Funds Universal Retirement S14</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRDCMJ4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Aviva Investors Emerging Markets Bond Fund Class Rmh Income</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPDX1K7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Aviva Investors Emerging Markets Local Currency Bond Fund R Accumulation</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFNRKF7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Aviva Investors Global Climate Credit Fund Class Ryh (GBP) Accumulation</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMZ3D97/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Aviva Investors Global Emerging Markets Core Class Ra Income</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD4TXN7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Aviva Investors Global Equity Endurance Fund Class R Accumulation</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDDN471/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Aviva Investors Global High Yield Bond Fund Class Rmh Income</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPDX1H4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Aviva Investors Global High Yield Bond Fund Class Rxh Income</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8S8346/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Aviva Investors Global Investment Grade Corporate Bond Fund Class Rmh Income</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPDX1L8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Aviva Investors Global Sovereign Bond Fund Class Rmh Income</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPDX1J6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Aviva Investors Natural Capital Global Equity Fund Class Ryh (GBP) Accumulation</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNG12D4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Aviva Investors ReturnPlus Fund Class Rqh Income</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BSHQLM5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Aviva Investors ReturnPlus Fund Class Ryh Accumulation</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BSHQLL4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Aviva Investors Sterling Liquidity Fund Class W Income</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRJ7SG2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Aviva Investors Sterling Liquidity Plus Fund Class 1 Accumulation</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B24F3S3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Continental European Equity Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0446132/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Global Climate Aware Equity Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BLNQ197/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Global Equity Endurance Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYXHPJ9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Global Equity Income Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3044209/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Global Equity Income Class 2 Income</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B9LCNW0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Higher Income Plus Class 2 Income</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0853130/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds International Index Tracking Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2NRNX5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Managed High Income Class 2 Income</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0446303/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Multi-Asset Core I Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMGWGY9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Multi-Asset Core II Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMGWH13/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Multi-Asset Core III Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMGWH46/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Multi-Asset Core IV Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMGWH79/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Aviva Investors UK Funds Multi-Asset Core V Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMGWHB3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Framlington UK Select Opportunities Class Z Income</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7MQVP6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Framlington UK Select Opportunities Class ZI Accumulation</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7FD4C2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Framlington UK Select Opportunities Class ZI Income</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B703ZS0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Framlington UK Smaller Companies Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7MMLM1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Framlington UK Smaller Companies Class Z Income</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRJZVS9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Framlington UK Sustainable Equity Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B51R123/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Framlington UK Sustainable Equity Class Z Income</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B55S4R8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global Distribution Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0830906/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global Distribution Class Z Income</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0830898/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global High Yield Class Z Gross Accumulation</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B29NGF0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global High Yield Class Z Gross Income</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B29NG94/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global Short Duration Bond Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDFZQV3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global Short Duration Bond Class Z Income</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDFZQW4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global Strategic Bond Class Z Acc Accumulation</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMZCH47/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global Strategic Bond Class Z Inc Income</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMZCH36/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global Sustainable Managed Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7MMHK1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Global Sustainable Managed Class Z Income</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7MQY79/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Green Short Duration Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNNDLG9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Green Short Duration Class Z Income</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNNDLH0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA People &amp; Planet Equity Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4490M2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA People &amp; Planet Equity Class Z Income</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B403RF0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Sterling Corporate Bond Class Z Gross Accumulation</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1Z48Z4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Sterling Corporate Bond Class Z Gross Income</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1Z48X2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Sterling Credit Short Duration Bond Class Z Gross Accumulation</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B5L2N22/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA Sterling Credit Short Duration Bond Class Z Gross Income</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B5VL0B7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA UK Equity Income Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7KBNV3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA UK Equity Income Class Z Income</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8HHY29/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA UK Equity Income Class Zm Accumulation</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRXFYM0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA UK Equity Income Class Zm Income</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRXFYN1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA US Short Duration High Yield Class Z Gross Accumulation</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B59VLT4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>BNP Paribas Asset Management AXA US Short Duration High Yield Class Z Gross Income</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B5TX5Q5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>BNP Paribas Flexi I US Mortgage Privilege Class H Accumulation</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BZ6FCB8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>BNP Paribas Parvest Equity Russia Priv Class H Income</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BZ12300/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>BNP Paribas Parvest Equity USA Small Cap Priv Accumulation</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF5CKY9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>BNY Mellon Absolute Return Bond (IE) Class W Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP4JQX2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>BNY Mellon Asian Income (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8KT3V4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>BNY Mellon Asian Income (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8KPW26/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>BNY Mellon Asian Opportunities (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8GJF67/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>BNY Mellon Asian Opportunities (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8GBZY1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>BNY Mellon Brazil Equity (IE) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B90P308/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>BNY Mellon Efficient Global High Yield Beta (IE) Sterling W Accumulation</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMYM6D0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>BNY Mellon Efficient Global High Yield Beta (IE) Sterling W Income</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMYM6F2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>BNY Mellon Efficient US High Yield Beta (IE) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYZ8Y26/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>BNY Mellon Emerging Income (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8GGF46/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>BNY Mellon Emerging Income (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8HMC86/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>BNY Mellon Emerging Market Corporate Debt (IE) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B5MQD78/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>BNY Mellon Emerging Markets Debt Local Currency (IE) Class W Income</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B91ZP89/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>BNY Mellon Emerging Markets Debt Total Return (IE) Class W Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD9PY59/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>BNY Mellon European Opportunities (Responsible) (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4Q5KM8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>BNY Mellon European Opportunities (Responsible) (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B881HQ5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>BNY Mellon Multi-Asset Global Balanced (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD8YW19/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>BNY Mellon Multi-Asset Growth (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8454P9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>BNY Mellon Multi-Asset Growth (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B87BSD0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>BNY Mellon Multi-Asset Income (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP851Q4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>BNY Mellon Multi-Asset Income (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP851R5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>BNY Mellon Multi-Asset Moderate (GB) Class W  Accumulation</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRJTS68/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>BNY Mellon Multi-Asset Moderate (GB) Class W  Income</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRJTWL1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>BNY Mellon Real Return (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8GG4B6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>BNY Mellon Real Return (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7W3652/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>BNY Mellon Real Return Fund (Responsible) (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD6DRD5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>BNY Mellon Real Return Fund (Responsible) (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD6DRF7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>BNY Mellon Responsible Horizons UK Corporate Bond (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8KDLX4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>BNY Mellon Responsible Horizons UK Corporate Bond (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8KCZN9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>BNY Mellon Strategic Bond Fund (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMD5328/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>BNY Mellon Strategic Bond Fund (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMD5339/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>BNY Mellon UK Equity (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6X4W59/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>BNY Mellon UK Equity (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8GHL29/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>BNY Mellon UK Income (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7M90R0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>BNY Mellon UK Income (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7W2G37/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>BNY Mellon UK Opportunities (Responsible) (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8HQWK0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>BNY Mellon UK Opportunities (Responsible) (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7RLX83/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>BNY Mellon US Equity Income (GB) Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGV53H3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>BNY Mellon US Equity Income (GB) Class W Income</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGV53J5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>BNY Mellon US Equity Income (IE) Class W Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD7Y0G1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>BNY Mellon US Equity Income (IE) Class W Income</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD5M755/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Baillie Gifford American Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0606196/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Baillie Gifford American Class B Income</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0606185/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Baillie Gifford China Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B39RMM8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Baillie Gifford China Class B Income</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3K73F7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Developed Asia Pacific Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3049204/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Developed Asia Pacific Class B Income</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3049163/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Emerging Markets Growth Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0602064/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Emerging Markets Growth Class B Income</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0602053/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Emerging Markets Leading Companies Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B06HZN2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Emerging Markets Leading Companies Class B Income</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B06HZP4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Emerging Markets Leading Companies Class W6 Accumulation</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BS52L92/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Emerging Markets Leading Companies Class W6 Income</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BS52LB4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Baillie Gifford European Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0605825/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Baillie Gifford European Class B Income</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0605739/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Global Alpha Growth Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B61DJ02/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Global Alpha Growth Class B Income</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3PPZ72/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Global Discovery Fund Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0605933/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Global Discovery Fund Class B Income</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0605922/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Global Income Growth Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0577247/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Global Income Growth Class B Income</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0577258/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Baillie Gifford High Yield Bond Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1W0GF1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Baillie Gifford High Yield Bond Class B Income</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3081671/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Baillie Gifford International Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0594127/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Baillie Gifford International Class B Income</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0594031/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Investment Grade Bond Class B Income</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr"/>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3081648/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Barings International Ireland Ltd Global Investment Grade Credit Tranche I Income</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQYL0H7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Barings International Ireland Ltd Global Resources Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4V6GM8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Barings International Ireland Ltd Hong Kong China Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3YV5X7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Barings International Ireland Ltd Latin America Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B64MCJ6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Barwon Investment Partners PTY Ltd Pareturn Barwon Listed Private Equity Founder G - B Accumulation</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr"/>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0889740/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) Advantage World Equity Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr"/>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BSLNFL9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) Tactical Opportunities Class D Accumulating GBP Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr"/>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK4PZT4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares China CNY Bond Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr"/>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMYX8V5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Developed Real Estate Index Class D Accumulating GBP Accumulation</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNDXYD7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Developed Real Estate Index Class D Hedged Income</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKPWSS4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Developed Real Estate Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFWVNS4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Developed World ESG Screened Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYZ8K06/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Developed World Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD0NCL4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Developed World Index Class D Hedged Income</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGL8877/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Emerging Markets Government Bond Index Class D Hedged Income</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKFVZB3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Emerging Markets Index Inst Accumulation</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3D07H3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Emerging Markets Index Inst Income</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr"/>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3D07L7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares GiltTrak Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD0NC25/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Global Aggregate 1-5 Year Bond Index Class D Hedged Income</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF2MW57/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Global Inflation-Linked Bond Index Class D Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr"/>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN6RDL7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Green Bond Index Class D Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr"/>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD5GZQ4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Green Bond Index Class D Hedged Income</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMTMD89/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares Screened Global Corporate Bond Index Class D Hedged Income</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr"/>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJN4RF5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares UK Credit Bond Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr"/>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD0NC47/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares UK Credit Bond Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr"/>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGWKS38/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>BlackRock (Dublin) iShares UK Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr"/>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD0NCQ9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF AI Innovation Class D2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr"/>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMY3H41/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Asian Dragon Class D4 Income</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B72VKS7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Asian Growth Leaders Class D2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr"/>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP25SS1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Asian High Yield Bond Class D3 Hedged Income</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr"/>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMDHV97/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Emerging Markets Local Currency Bond Class D2 Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr"/>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3W47C1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Euro Bond Class D4 Income</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr"/>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8J3JZ3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Euro Short Duration Bond Class D3 Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7W0QJ7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Euro-Markets Class D4 Income</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr"/>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8209Y0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF European Class D4 Income</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr"/>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B89V0M1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF European Equity Income Class D5G Hedged Income</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr"/>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BBVHRJ4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF European Value Class D4 Income</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7T4QJ2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Fixed Income Global Opportunities Class D2 Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1PF5P6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Global Allocation Class D2 Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8DRW63/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>BlackRock (Lux) BGF Global Corporate Bond Class D2 Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr"/>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWXT999/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>BlackRock Consensus 70 Class D Acc Accumulation</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B86MM21/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>BlackRock Consensus 85 Class D Acc Accumulation</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8D0SR5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>BlackRock Continental European Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4VY989/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>BlackRock Continental European Class D Income</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6YTYJ1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>BlackRock Continental European Income Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3S9LG2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>BlackRock Continental European Income Class D Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWG0717/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>BlackRock Continental European Income Class D Hedged Income</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr"/>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWG07G2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>BlackRock Continental European Income Class D Income</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr"/>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3Y7MQ7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>BlackRock Corporate Bond 1 - 10 Year Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B84DT14/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>BlackRock Corporate Bond Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr"/>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4QC331/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>BlackRock Corporate Bond Class D Income</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4T5JV7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>BlackRock Developed Markets Sustainable Equity Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4XLYS3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>BlackRock Developed Markets Sustainable Equity Class D Income</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8DDP95/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>BlackRock Dynamic Allocation Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BVYJ3Y4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>BlackRock Dynamic Diversified Growth Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B823TT4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>BlackRock Dynamic Diversified Growth Class D Income</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B883P12/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>BlackRock ESG Strategic Growth Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFWY6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>BlackRock Emerging Markets Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4R9F68/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>BlackRock Emerging Markets Class D Income</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B88T662/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>BlackRock European Absolute Alpha Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4Y62W7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>BlackRock European Dynamic Class FD Accumulation</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BCZRNN3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>BlackRock European Dynamic Class FD Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWG05X5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>BlackRock European Dynamic Class FD Hedged Income</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWG05Z7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>BlackRock European Dynamic Class FD Income</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BCZRNM2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>BlackRock Global Equity NURS II Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8BTNJ1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>BlackRock Global Income Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3L7Q24/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>BlackRock Global Income Class D Income</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3VXK75/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>BlackRock Global Unconstrained Equity Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFK3ML8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>BlackRock Gold and General Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B5ZNJ89/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>BlackRock Gold and General Class D Income</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B5ZNJ90/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>BlackRock Institutional Cash Series ICS Sterling Government Liquidity Premier Accumulation</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B43PVC8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>BlackRock Institutional Cash Series ICS Sterling Liquid Environmentally Aware Premier Accumulation</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKC9GJ5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>BlackRock Institutional Cash Series ICS Sterling Liquidity Premier Accumulation</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B43FT80/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>BlackRock Institutional Cash Series ICS Sterling Liquidity Premier T1 Inc Income</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRJSTS4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>BlackRock Institutional Cash Series ICS Sterling Ultra Short Bond Premier GBP Income</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFZD235/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>BlackRock Market Advantage Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BS7K666/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 3 Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFYB7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 3 Class D Income</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFYC8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 3 Select ESG Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN090Q3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 4 Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFYJ5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 4 Class D Income</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFYK6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 5 Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFYQ2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 5 Class D Income</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFYR3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 5 Select ESG Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr"/>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFYX9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 6 Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFZ14/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 6 Class D Income</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFZ25/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 7 Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BV49YS5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>BlackRock MyMap 8 Select ESG Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN090M9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>BlackRock Natural Resources Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6865B7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>BlackRock Natural Resources Class D Income</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B46KYQ5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Index Linked Gilt Index Class H Accumulation</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPFJDG3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Japan Equity ESG Screened and Optimised Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN09074/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Japan Equity ESG Screened and Optimised Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN09085/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Japan Equity Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6QQ9X9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Japan Equity Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN08Z76/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Japan Equity Index Class H Accumulation</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJL5BZ8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Mid Cap UK Equity Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7VT093/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Mid Cap UK Equity Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNB74C0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>BlackRock iShares North American Equity Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7QK1Y3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>BlackRock iShares North American Equity Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN08ZT8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>BlackRock iShares North American Equity Index Class H Accumulation</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPFJD41/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Over 15 Years Corporate Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFX32/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Over 15 Years Gilts Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF338G2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Overseas Government Bond Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B849C80/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Overseas Government Bond Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN091P9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Overseas Government Bond Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN091Q0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Overseas Government Bond Index Class H Accumulation</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPFJD85/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Pacific Ex Japan Equity ESG Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN090H4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Pacific Ex Japan Equity ESG Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN090J6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Pacific ex Japan Equity Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B849FB4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Pacific ex Japan Equity Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BV49YW9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>BlackRock iShares Pacific ex Japan Equity Index Class H Accumulation</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJL5C00/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>BlackRock iShares S&amp;P 500 Equal Weight Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRTCS34/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>BlackRock iShares UK Equity ESG Screened and Optimised Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN08ZV0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>BlackRock iShares UK Equity ESG Screened and Optimised Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN08ZW1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>BlackRock iShares UK Equity Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7C44X9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>BlackRock iShares UK Equity Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFBFVX8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>BlackRock iShares UK Equity Index Class H Accumulation</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPFJDB8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>BlackRock iShares UK Gilts All Stocks Index Class D Accumulation</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B83HGR2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>BlackRock iShares UK Gilts All Stocks Index Class D Income</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B89VCR0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>BlueBay Global High Yield ESG Bond Class C Income</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP2C280/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>BlueBay Impact Aligned Bond Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMB54V6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>BlueBay Impact Aligned Bond Class G Accumulation</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNG2HY3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>BlueBay Impact Aligned Bond Class G Q Income</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNG2LG3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Brandes Brandes European Value Fund Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3157505/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Brandes Brandes European Value Fund Class I1 Income</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYXWTN6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Brandes Brandes Global Value Fund Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3237827/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Brandes Brandes Global Value Fund Class I1 Income</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1SHJJ1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Brandes Brandes U.S. Value Fund Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3157561/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Brickwood TM Brickwood Global Value Class R Accumulation</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BTKVZL1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>CT American Class Z Income</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6WD1G1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>CT American Select Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7HJLD8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>CT American Select Class Z Income</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8BC196/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>CT American Smaller Companies Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8358Z8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>CT American Smaller Companies Class Z Income</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B88YT35/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>CT Asia Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B83BWC1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>CT CT Multi-Manager Universal Adventurous B Accumulation</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B898743/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>CT CT Multi-Manager Universal Adventurous B Income</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4YRDJ4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>CT CT Multi-Manager Universal Cautious B Accumulation</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B83XVS6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>CT CT Multi-Manager Universal Cautious B Income</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4YQGY7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>CT CT Multi-Manager Universal Defensive B Accumulation</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BG5GMB9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>CT CT Multi-Manager Universal Defensive B Income</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BG5GM97/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>CT CT Multi-Manager Universal Growth B Accumulation</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7S6RS5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>CT CT Multi-Manager Universal Growth B Income</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B503GT4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>CT Dollar Bond Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B87D999/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>CT Dollar Bond Class Z Income</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B9BRCL7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>CT Dynamic Real Return Class S Accumulation</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWWC6P4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>CT Dynamic Real Return Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B93TQ86/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>CT Dynamic Real Return Class Z Income</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B93MKD8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>CT Emerging Market Bond Class Z Gross Income</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B82D756/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>CT Emerging Market Bond Class Z Income</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B817DW8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>CT European Bond Class Z Income</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B990YR8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>CT European Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8C2LS4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>CT European Select Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8BC5H2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>CT European Select Class Z Income</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B98WQ46/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>CT European Smaller Companies Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B84CYY9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>CT European Smaller Companies Class Z Income</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B978SQ1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>CT FTSE All-Share Tracker 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3313813/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>CT FTSE All-Share Tracker 2 Income</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0846464/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>CT Global Bond Class Z (Gross) Income</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8844J6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>CT Global Bond Class Z Income</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8C2M70/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>CT Global Emerging Markets Equity Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8BYHK5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>CT Global Equity Income Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B99MQF6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>CT Global Equity Income Class Z Income</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7S8N05/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>CT Global Equity-Linked UK Inflation 3 Accumulation</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4NVY38/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>CT Global Extended Alpha Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3B0F60/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>CT Global Focus ZA Accumulation</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF0Q8K8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>CT Global Multi Asset Income Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNG6455/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>CT Global Multi Asset Income Class Z Income</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNG6466/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>CT Global Real Estate Securities 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJ05NG4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>CT Global Select Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8C2TM4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>CT Global Social Bond Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKSBMM0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>CT Global Social Bond Class Z Income</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKSBMN1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>CT Global Total Return Bond (GBP Hedged) C Accumulation</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B80KFS8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>CT Global Total Return Bond (GBP Hedged) C Income</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B80KHR1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>CT High Yield Bond Class Z (Gross) Accumulation</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B82VC22/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>CT High Yield Bond Class Z (Gross) Income</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B99MVQ2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>CT High Yield Bond Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPZ55D2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>CT High Yield Bond Class Z Income</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7SGDT8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>CT Japan Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7TRT70/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>CT Sustainable Opportunities Global Equity C Accumulation</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYZ62V5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>CT Sustainable Universal MAP Adventurous C Accumulation</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMW8RH1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>CT Sustainable Universal MAP Balanced C Accumulation</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr"/>
+      <c r="C481" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKV4486/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>CT Sustainable Universal MAP Cautious C Accumulation</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr"/>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKV4464/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>CT Sustainable Universal MAP Defensive C Accumulation</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr"/>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMW8RF9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>CT Sustainable Universal MAP Growth C Accumulation</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr"/>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKV44B9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>CT UK Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B84PM55/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>CT UK Class Z Income</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B84PMM2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>CT UK Commercial Property 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr"/>
+      <c r="C487" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B830G15/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>CT UK Commercial Property 2 Income</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr"/>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6449M4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>CT UK Commercial Property Feeder 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr"/>
+      <c r="C489" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWZMHM5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>CT UK Commercial Property Feeder 2 Income</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr"/>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWZMHL4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>CT UK Equity Alpha Income Class Z Income</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr"/>
+      <c r="C491" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B88P6D7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>CT UK Equity Income 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr"/>
+      <c r="C492" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7TFC97/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>CT UK Equity Income 2 Income</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B60HHR8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>CT UK Equity Income Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B888FR3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>CT UK Equity Income Class Z Income</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr"/>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8169Q1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>CT UK Growth and Income Class Z Income</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr"/>
+      <c r="C496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8848T4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>CT UK Institutional Class 2 Accumulation</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr"/>
+      <c r="C497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0145161/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>CT UK Mid 250 Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr"/>
+      <c r="C498" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8BX5X1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>CT UK Monthly Income Class Z Income</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr"/>
+      <c r="C499" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8BV450/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>CT UK Property Authorised Investment Fund AIF Inst Accumulation</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr"/>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQ1YHV2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>CT UK Property Authorised Investment Fund AIF Inst Income</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr"/>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQ1YHW3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>CT UK Property Authorised Trust Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQ3G0Y0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>CT UK Property Authorised Trust Class I Income</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQ3G0Z1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>CT UK Smaller Companies Class Z Income</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7JL4Y4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>CT UK Social Bond Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr"/>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF233D5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>CT UK Social Bond Class IG Income</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr"/>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF233G8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>CT UK Social Bond Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr"/>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF23379/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>CT UK Social Bond Class Z GROSS Accumulation</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr"/>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF23380/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>CT UK Social Bond Class Z GROSS Income</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr"/>
+      <c r="C509" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF233B3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>CT UK Social Bond Class Z Income</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr"/>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF23391/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>CT UK Social Bond Inst Accumulation</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr"/>
+      <c r="C511" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF233C4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>CT UK Sustainable Equity Class IA Accumulation</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr"/>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJ5JM86/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>CT UK Sustainable Equity Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr"/>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BZ21SS9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>CT UK Sustainable Equity Class ZI Income</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr"/>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BZ21ST0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>CT US Equity Income Class Z Income</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr"/>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BZ563P3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>CT US Equity Income Class ZNA Accumulation</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr"/>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD37PD6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>CT US Smaller Companies C Income</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7YDFB9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>CT Universal MAP Adventurous C Accumulation</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr"/>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK5Z9G8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>CT Universal MAP Balanced C Accumulation</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr"/>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF99W06/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>CT Universal MAP Cautious C Accumulation</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr"/>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF99VY3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>CT Universal MAP Defensive C Accumulation</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+      <c r="C521" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK5Z9D5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>CT Universal MAP Growth C Accumulation</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr"/>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF99W28/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>CT Universal MAP Income C Accumulation</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr"/>
+      <c r="C523" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK5ZC69/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>CT Universal MAP Income C Income</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr"/>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BK5ZC81/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Calamos Global Convertible Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B66CN79/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Calamos Global Convertible Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr"/>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKRVJH5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Calamos Global Convertible Class Z Income</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr"/>
+      <c r="C527" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKRVJG4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Canaccord Genuity Wealth Management Canaccord Genuity Dynamic Class A Accumulation</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr"/>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BTJ03D7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Capital Group Global Equity (LUX) Class Zd Income</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr"/>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B9N5521/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities (LUX) Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr"/>
+      <c r="C530" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B79J0V7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities (LUX) Class Zd Income</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr"/>
+      <c r="C531" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7VH3C1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities (LUX) Class Zdh-GBP Income</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr"/>
+      <c r="C532" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8P48Z3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities (LUX) Class Zgd Income</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr"/>
+      <c r="C533" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7XYJM2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities (LUX) Class Zgdh-GBP Income</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr"/>
+      <c r="C534" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7SF6L8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities (LUX) Class Zh-GBP Accumulation</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr"/>
+      <c r="C535" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B88XFP6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities Class P Accumulation</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr"/>
+      <c r="C536" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP38YG9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities Class P Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr"/>
+      <c r="C537" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPCJ6B2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities Class P Hedged Income</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr"/>
+      <c r="C538" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPCJ6S9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Capital Group Global High Income Opportunities Class P Income</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr"/>
+      <c r="C539" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPCJ6R8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Capital Group Investment Company of America (LUX) Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr"/>
+      <c r="C540" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD2MVX4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Capital Group Investment Company of America (LUX) Class Zd Income</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr"/>
+      <c r="C541" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD2MW20/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Capital Group Investment Company of America (LUX) Class Zdh-GBP Income</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
+      <c r="C542" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD2MW53/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Capital Group Investment Company of America (LUX) Class Zgd Income</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr"/>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD2MW86/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Capital Group Investment Company of America (LUX) Class Zgdh-GBP Income</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr"/>
+      <c r="C544" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD2MWC0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Capital Group Investment Company of America (UK) Class P Accumulation</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRBTFM1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Capital Group Japan Equity (LUX) Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+      <c r="C546" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B9FHXD2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Capital Group Japan Equity (LUX) Class Zd Income</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr"/>
+      <c r="C547" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7YLBW6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Capital Group Japan Equity (LUX) Class Zgdh-GBP Income</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr"/>
+      <c r="C548" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BBH7WC6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Capital Group Japan Equity (LUX) Class Zh-GBP Accumulation</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
+      <c r="C549" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BBH7W71/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Capital Group New Perspective Fund (LUX) Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
+      <c r="C550" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYSR077/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Capital Group New Perspective Fund (LUX) Class Zd Income</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr"/>
+      <c r="C551" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYSR0F5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Capital Group New Perspective Fund (LUX) Class Zgd Income</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr"/>
+      <c r="C552" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYSR0M2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Capital Group New Perspective Fund (LUX) Class Zh-GBP Accumulation</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr"/>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYSR0T9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Capital Group New Perspective Fund (UK) Class P Acc GBP Accumulation</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr"/>
+      <c r="C554" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BS3F739/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Capital Group New Perspective Fund (UK) Class P Inc GBP Income</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr"/>
+      <c r="C555" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BS3F740/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Capital Group US Corporate Bond (LUX) Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr"/>
+      <c r="C556" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD5D9M9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Capital Group US Corporate Bond (LUX) Class Zd Income</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr"/>
+      <c r="C557" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD5D9T6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Capital Group US Corporate Bond (LUX) Class Zgd Income</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr"/>
+      <c r="C558" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD5DB01/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Capital Group US High Yield Fund (LUX) Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr"/>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF0L2M3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Capital Group US High Yield Fund (LUX) Class Zd Income</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr"/>
+      <c r="C560" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF0L2T0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Capital Group US High Yield Fund (LUX) Class Zgd Income</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr"/>
+      <c r="C561" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF0L2Z6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Capital Group World Dividend Growers (LUX) Class Z Accumulation</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr"/>
+      <c r="C562" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BBH7ZN8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Capital Group World Dividend Growers (LUX) Class Zd Income</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr"/>
+      <c r="C563" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BBH7ZS3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Carmignac Carmignac Portfolio Asia Discovery Class FW GBP Acc Accumulation</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr"/>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGP6SY4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Carmignac Carmignac Portfolio Emergents Class FW GBP Acc Accumulation</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr"/>
+      <c r="C565" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGP6SV1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Carmignac Carmignac Portfolio Global Bond Class FW GBP Acc Accumulation</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr"/>
+      <c r="C566" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGP6T63/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Carmignac Carmignac Portfolio Global Bond Class FW GBP Acc Hdg Accumulation</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr"/>
+      <c r="C567" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B46K5H3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Carmignac Carmignac Portfolio Grande Europe Class FW GBP Acc Accumulation</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr"/>
+      <c r="C568" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMW2PM4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Carmignac Carmignac Portfolio Long Short European Equities Class F Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr"/>
+      <c r="C569" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGP6T41/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Carmignac Carmignac Portfolio Patrimoine Class F Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr"/>
+      <c r="C570" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGP6TG3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Carne Global Fund Managers CG AJ Bell Adventurous Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr"/>
+      <c r="C571" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYW8VG2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Carne Global Fund Managers CG AJ Bell Adventurous Class I Income</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr"/>
+      <c r="C572" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYW8T68/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Carne Global Fund Managers CG AJ Bell Balanced Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr"/>
+      <c r="C573" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYW8RX1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Carne Global Fund Managers CG AJ Bell Cautious Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr"/>
+      <c r="C574" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYW8RV9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Carne Global Fund Managers CG AJ Bell Global Growth Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr"/>
+      <c r="C575" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD833W4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Carne Global Fund Managers CG AJ Bell Income &amp; Growth Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr"/>
+      <c r="C576" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BH3W788/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Carne Global Fund Managers CG AJ Bell Income &amp; Growth Class I Income</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr"/>
+      <c r="C577" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BH3W799/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Carne Global Fund Managers CG AJ Bell Income Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr"/>
+      <c r="C578" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BH3W744/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Comgest Comgest Growth Japan GBP I Acc Class Accumulation</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr"/>
+      <c r="C579" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYYLQ19/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Courtiers Ethical Value Equity Class R Accumulation</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr"/>
+      <c r="C580" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNG93X5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Courtiers Global (Ex UK) Equity Income Class R Accumulation</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr"/>
+      <c r="C581" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYXVV60/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Courtiers Investment Grade Bond Class R Accumulation</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr"/>
+      <c r="C582" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYXVV71/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Courtiers Total Return Balanced Risk Accumulation</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr"/>
+      <c r="C583" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1P2K63/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Courtiers Total Return Cautious Risk Accumulation</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr"/>
+      <c r="C584" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1P2K41/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Courtiers Total Return Growth Accumulation</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr"/>
+      <c r="C585" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1P2K85/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Courtiers UK Equity Income  Class R Accumulation</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr"/>
+      <c r="C586" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYXVV59/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Credo Credo Dynamic Class A Accumulation</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr"/>
+      <c r="C587" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDFZR65/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Credo Credo Global Equity Class A Accumulation</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr"/>
+      <c r="C588" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDFZR87/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>DMS DMS Stirling House Balanced Fund Class R Accumulation</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr"/>
+      <c r="C589" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B99R167/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>DMS DMS Stirling House Balanced Fund Class R Income</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr"/>
+      <c r="C590" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B99R178/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>DMS DMS Stirling House Dynamic Fund Class R Accumulation</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr"/>
+      <c r="C591" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B99R189/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>DMS DMS Stirling House Growth Fund Accumulation</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr"/>
+      <c r="C592" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B99R145/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>DMS DMS Stirling House Growth Fund Income</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr"/>
+      <c r="C593" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B99R156/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Dimensional Emerging Markets Core Equity Lower Carbon ESG Screened GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr"/>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BLCGQW6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Dimensional Emerging Markets Core Equity Lower Carbon ESG Screened GBP Distributing Shares Income</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr"/>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BLCGQX7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Dimensional European Value GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr"/>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B1W6CY0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Dimensional Global Core Equity GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr"/>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PC048/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Dimensional Global Core Fixed Income GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr"/>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BG85LL6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Dimensional Global Short Fixed Income Lower Carbon ESG Screened GBP Accumulation Accumulation</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr"/>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNKL9M8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Dimensional Global Targeted Value GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr"/>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PC093/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Dimensional Global Targeted Value Lower Carbon ESG Screened GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr"/>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQQ8LB7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Dimensional Global Value GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr"/>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3NVPH2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Dimensional International Core Equity GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr"/>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B23YLH6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Dimensional International Value GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr"/>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/3377228/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Dimensional US Small Companies GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr"/>
+      <c r="C605" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B0701B0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Dimensional World Allocation 40/60 GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr"/>
+      <c r="C606" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B56FVB1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Dimensional World Allocation 40/60 GBP Distributing Shares Income</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr"/>
+      <c r="C607" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B5KL2L2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Dimensional World Allocation 60/40 GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr"/>
+      <c r="C608" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B416SD3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Dimensional World Allocation 80/20 GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr"/>
+      <c r="C609" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYTYV18/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Dimensional World Equity GBP Accumulation Shares Accumulation</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr"/>
+      <c r="C610" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3Z8MM5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Dimensional World Equity Lower Carbon ESG Screened GBP Accumulation Accumulation</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr"/>
+      <c r="C611" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQ5J6K5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Dimensional World Equity Lower Carbon ESG Screened GBP Distributing Income</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr"/>
+      <c r="C612" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQ5J6L6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Dodge &amp; Cox Worldwide Funds Plc Dodge &amp; Cox Worldwide Funds plc - Global Bond Fund GBP Distributing Class (H) Income</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr"/>
+      <c r="C613" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BLG2YK4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Dodge &amp; Cox Worldwide Funds Plc Dodge &amp; Cox Worldwide Funds plc - Global Bond Fund GBP Distributing Class Income</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr"/>
+      <c r="C614" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B556C01/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Dodge &amp; Cox Worldwide Funds Plc Dodge &amp; Cox Worldwide Funds plc - Global Stock Fund GBP Accumulating Class Accumulation</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr"/>
+      <c r="C615" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B54J687/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Dodge &amp; Cox Worldwide Funds Plc Dodge &amp; Cox Worldwide Funds plc - Global Stock Fund GBP Distributing Class (H) Income</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr"/>
+      <c r="C616" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYVQ3H2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Dodge &amp; Cox Worldwide Funds Plc Dodge &amp; Cox Worldwide Funds plc - Global Stock Fund GBP Distributing Class Income</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr"/>
+      <c r="C617" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B54PSJ0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Dodge &amp; Cox Worldwide Funds Plc Dodge &amp; Cox Worldwide Funds plc - U.S. Stock Fund GBP Accumulating Class Accumulation</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr"/>
+      <c r="C618" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B50M4X1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>EdenTree Green Future Class B Income</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr"/>
+      <c r="C619" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BP5FBP6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>EdenTree Green Infrastructure Class B Income</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr"/>
+      <c r="C620" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BNG5Z71/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>EdenTree Green Infrastructure Class I Accumulation</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr"/>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BQMRSF1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>EdenTree Short Dated Bond Fund Class B Income</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr"/>
+      <c r="C622" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BZ012J0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>EdenTree Sterling Bond Fund Class B Income</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr"/>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B2PF8D2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>EdenTree Sustainable European Equity Fund Class B Income</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr"/>
+      <c r="C624" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0844833/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>EdenTree Sustainable Global Equity Fund Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr"/>
+      <c r="C625" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BVTDCW2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>EdenTree Sustainable Global Equity Fund Class B Income</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr"/>
+      <c r="C626" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0844907/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>EdenTree Sustainable Managed Income Class B Income</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr"/>
+      <c r="C627" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0944971/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>EdenTree UK Equity Fund Class B Income</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr"/>
+      <c r="C628" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0937175/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>EdenTree UK Equity Opportunities Class B Income</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr"/>
+      <c r="C629" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/0844606/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Epic Funds Global Equity Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr"/>
+      <c r="C630" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFNBK71/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Evelyn Adventurous Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr"/>
+      <c r="C631" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX8KW0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Evelyn Adventurous Portfolio Clean Income</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr"/>
+      <c r="C632" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX8KX1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Evelyn Balanced Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr"/>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFY1NH1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Evelyn Balanced Portfolio Clean Income</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr"/>
+      <c r="C634" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFY1NJ3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Evelyn Cautious Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr"/>
+      <c r="C635" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX8KN1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Evelyn Cautious Portfolio Clean Income</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr"/>
+      <c r="C636" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX8LF0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Evelyn Conservative Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr"/>
+      <c r="C637" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFY1MG3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Evelyn Conservative Portfolio Clean Income</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr"/>
+      <c r="C638" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFY1MH4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Evelyn Defensive Growth Class K Income</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr"/>
+      <c r="C639" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BN48KQ6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Evelyn Defensive Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr"/>
+      <c r="C640" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX8KL9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Evelyn Defensive Portfolio Clean Income</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr"/>
+      <c r="C641" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX8KM0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Evelyn Growth Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr"/>
+      <c r="C642" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX8KR5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Evelyn Growth Portfolio Clean Income</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr"/>
+      <c r="C643" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX8KS6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Evelyn Horizon Adventurous Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr"/>
+      <c r="C644" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMYX3Z4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Evelyn Horizon Adventurous Portfolio Clean Income</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr"/>
+      <c r="C645" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMYX406/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Evelyn Horizon Cautious Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr"/>
+      <c r="C646" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX8L38/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Evelyn Horizon Cautious Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr"/>
+      <c r="C647" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMW2DT7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Evelyn Horizon Cautious Portfolio Clean Accumulation</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr"/>
+      <c r="C648" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMW2DS6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>FP Russell Investments Limited UK Growth Assets Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr"/>
+      <c r="C649" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4L1FT3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>FP Russell Investments Limited UK Growth Assets Class C Income</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr"/>
+      <c r="C650" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B4KT286/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>FP WHEB FP WHEB Sustainability Impact Fund Class C Accumulation</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr"/>
+      <c r="C651" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8HPRW4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>FP WHEB FP WHEB Sustainability Impact Fund Class C Income</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr"/>
+      <c r="C652" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BHBFFN0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>FSSA IM All China Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr"/>
+      <c r="C653" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BZCCYN9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>FSSA IM All China Class E Accumulation</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr"/>
+      <c r="C654" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BGMHMT3/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>FSSA IM Asia Focus Class B Accumulation</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr"/>
+      <c r="C655" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BWNGXJ8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>FSSA IM Asian Equity Plus Class III Income</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr"/>
+      <c r="C656" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B97LZ36/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>FSSA IM China A Shares Class VI Accumulation</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr"/>
+      <c r="C657" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJN6RG2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>FSSA IM China Growth Class VI Income</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr"/>
+      <c r="C658" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDRM786/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>FTGF Brandywine Global Opportunistic Fixed Income Class X Income</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr"/>
+      <c r="C659" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B3TC289/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>FTGF ClearBridge Global Growth Leaders Class X Accumulation</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr"/>
+      <c r="C660" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BTHZ4D1/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>FTGF ClearBridge Infrastructure Value Class X Income</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr"/>
+      <c r="C661" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BDBBPZ2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>FTGF ClearBridge US Equity Sustainability Leaders Class X Accumulation</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr"/>
+      <c r="C662" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BZ1NPT6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>FTGF ClearBridge US Large Cap Growth Class X Accumulation</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr"/>
+      <c r="C663" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B241D36/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>FTGF Royce U.S. Small Cap Opportunity Class X Accumulation</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr"/>
+      <c r="C664" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B23Z8V2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>FTGF Royce U.S. Small Cap Opportunity Class X Income</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr"/>
+      <c r="C665" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B19Z499/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>FTGF Western Asset Global High Yield Class X Income</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr"/>
+      <c r="C666" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B53T7Z2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Federated Hermes (UK) LLP Federated Hermes Sterling Cash Plus Class 3 Accumulation</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr"/>
+      <c r="C667" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6TNT26/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Federated Hermes Asia ex-Japan Equity Class F (Hedged) Accumulation</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr"/>
+      <c r="C668" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BBL4VQ0/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Fidelity (Offshore) MSCI Europe Index Class P Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr"/>
+      <c r="C669" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX5MQ9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Fidelity (Offshore) MSCI Japan Index Class P Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr"/>
+      <c r="C670" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX5NF5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Fidelity (Offshore) MSCI Pacific ex-Japan Index Class P Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr"/>
+      <c r="C671" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD24Q91/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Fidelity (Offshore) MSCI World Index Class P Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr"/>
+      <c r="C672" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX5P48/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Fidelity (Offshore) S&amp;P 500 Index Class P Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr"/>
+      <c r="C673" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYX5MZ8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Allocator World Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr"/>
+      <c r="C674" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B9777B6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) American Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr"/>
+      <c r="C675" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B8GPC42/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) American Special Situations Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr"/>
+      <c r="C676" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B89ST70/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Asia Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr"/>
+      <c r="C677" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B6Y7NF4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Asia Class W Hedged Accumulation</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr"/>
+      <c r="C678" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BKDZ1H5/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Enhanced Income Class W Inc Income</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr"/>
+      <c r="C679" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B87HPZ9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) European Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr"/>
+      <c r="C680" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BFRT350/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) European Class W Income</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr"/>
+      <c r="C681" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7VNK95/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Global Dividend Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr"/>
+      <c r="C682" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7GJPN7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Global Dividend Class W Inc (monthly) shares Income</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr"/>
+      <c r="C683" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYSYZL7/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Global Dividend Class W Income</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr"/>
+      <c r="C684" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B777808/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Global Enhanced Income Class W Acc Accumulation</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr"/>
+      <c r="C685" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD1NLL6/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Global Enhanced Income Class W Inc (monthly) shares Income</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr"/>
+      <c r="C686" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BYSYZN9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Global Enhanced Income Class W Income Income</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr"/>
+      <c r="C687" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD1NLJ4/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>Fidelity (Onshore) Global Future Leaders Class W  Accumulation</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr"/>
+      <c r="C688" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BPLVMC2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Fortem Capital Limited Alternative Growth Class A Accumulation</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr"/>
+      <c r="C689" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BJ116W8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Fortem Capital Limited Capital Absolute Return  Class S Accumulation</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr"/>
+      <c r="C690" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMV8W22/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Fortem Capital Limited Capital Absolute Return  Class T Income</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr"/>
+      <c r="C691" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMV8W77/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Fortem Capital Limited Capital Dynamic Growth Class A (GBP) Accumulation</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr"/>
+      <c r="C692" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BRJL4C2/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Fortem Capital Limited Progressive Growth Class A Accumulation</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr"/>
+      <c r="C693" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BF04783/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Fortem Capital Limited Progressive Growth Class D Income</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr"/>
+      <c r="C694" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BD7Y3W8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Fortem Capital Limited US Equity Income Class F Hedged Income</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr"/>
+      <c r="C695" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/BMC2RM8/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Franklin Templeton (Lux) Franklin Global Growth Fund Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr"/>
+      <c r="C696" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7M3XD9/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Franklin Templeton (Lux) Franklin India Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr"/>
+      <c r="C697" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7TC339/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Franklin Templeton (Lux) Templeton Asian Growth Class W Accumulation</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr"/>
+      <c r="C698" s="2" t="inlineStr">
+        <is>
+          <t>https://www.direct.aviva.co.uk/wealth/FundChoice/SelfSelectFundsList/FundDetails/B7CPH77/SelfSelectFund</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C543" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C544" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C545" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C546" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C547" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C548" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C549" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C550" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C551" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C552" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C553" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C554" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C555" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C556" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C557" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C558" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C559" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C560" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C561" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C562" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C563" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C564" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C565" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C566" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C567" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C568" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C569" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C570" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C571" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C572" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C573" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C574" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C575" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C576" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C577" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C578" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C579" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C580" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C581" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C582" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C583" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C584" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C585" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C586" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C587" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C588" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C589" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C590" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C591" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C592" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C593" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C594" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C595" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C596" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C597" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C598" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C599" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C600" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C601" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C602" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C603" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C604" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C605" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C606" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C607" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C608" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C609" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C610" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C611" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C612" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C613" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C614" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C615" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C616" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C617" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C618" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C619" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C620" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C621" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C622" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C623" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C624" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C625" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C626" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C627" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C628" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C629" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C630" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C631" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C632" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C633" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C634" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C635" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C636" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C637" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C638" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C639" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C640" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C641" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C642" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C643" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C644" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C645" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C646" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C647" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C648" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C649" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C650" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C651" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C652" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C653" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C654" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C655" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C656" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C657" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C658" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C659" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C660" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C661" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C662" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C663" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C664" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C665" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C666" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C667" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C668" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C669" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C670" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C671" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C672" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C673" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C674" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C675" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C676" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C677" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C678" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C679" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C680" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C681" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C682" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C683" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C684" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C685" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C686" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C687" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C688" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C689" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C690" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C691" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C692" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C693" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C694" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C695" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C696" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C697" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C698" r:id="rId697"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>